--- a/school_counselor_forms/005_student_food_survey_template--school_counselor_forms.xlsx
+++ b/school_counselor_forms/005_student_food_survey_template--school_counselor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_question</t>
+          <t>usual_breakfast</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>second_question</t>
+          <t>usual_lunch</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>third_question</t>
+          <t>usual_dinner</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>first_food</t>
+          <t>food_preference</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Which food do you like first</t>
+          <t>Which food do you like most among the options?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>second_food</t>
+          <t>eating_habits_home</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Which food do you like second</t>
+          <t>How often do you eat at home?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>third_food</t>
+          <t>eating_habits_school</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Which food do you like third</t>
+          <t>How often do you eat at school?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>food_preferred</t>
+          <t>food_allergies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Which food you prefer</t>
+          <t>Do you have food allergies?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>food_not_preferred</t>
+          <t>food_restrictions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Which food you do not prefer</t>
+          <t>Do you have food restrictions?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>eating_habits</t>
+          <t>date_of_birth</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How often do you eat at home</t>
+          <t>What is your date of birth?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>eating_habits_home</t>
+          <t>time_of_meals</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How often do you eat home</t>
+          <t>What time do you usually have meals at home?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>eating_habits_school</t>
+          <t>food_choice</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How often do you eat school</t>
+          <t>How do you usually choose food?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,299 +791,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>food_allergies</t>
+          <t>page_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Do you have food allergies</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>food_restrictions</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Do you have food restrictions</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Date of Birth</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Date of birth</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>time_of_birth</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Time of birth</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>time_of_birth</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Time of birth</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>food_choice</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>How do you choose food</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>food_choice</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>How do you choose food</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>food_choice</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Food choice</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>food_choice</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>How do you choose food</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>food_choice</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Food choice</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>food_choice</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>How do you choose food</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>food_choice</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Food choice</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,10 +822,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +850,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>usual_breakfast_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +867,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>usual_breakfast_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +884,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>usual_breakfast_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +901,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>usual_breakfast_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +918,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>usual_breakfast_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +935,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>usual_breakfast_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +952,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>usual_lunch_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +969,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>usual_lunch_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +986,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>usual_lunch_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1003,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>usual_lunch_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1020,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>usual_lunch_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1037,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>usual_dinner_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1054,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>usual_dinner_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1071,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>usual_dinner_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1088,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>usual_dinner_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1105,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>usual_dinner_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1483,7 +1207,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>first_food_choices</t>
+          <t>food_preference_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1224,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>first_food_choices</t>
+          <t>food_preference_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1241,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>first_food_choices</t>
+          <t>food_preference_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1258,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>first_food_choices</t>
+          <t>food_preference_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1275,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>first_food_choices</t>
+          <t>food_preference_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1292,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>first_food_choices</t>
+          <t>food_preference_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,357 +1309,68 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>second_food_choices</t>
+          <t>food_allergies_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>pizza</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>pizza</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>second_food_choices</t>
+          <t>food_allergies_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>salad</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>salad</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>second_food_choices</t>
+          <t>food_restrictions_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sandwich</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sandwich</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>second_food_choices</t>
+          <t>food_restrictions_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>soup</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>soup</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>second_food_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>mac_and_cheese</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>mac and cheese</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>third_food_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>chicken</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>chicken</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>third_food_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>beef</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>beef</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>third_food_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>pasta</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>third_food_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>vegetables</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>vegetables</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>third_food_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>salad</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>salad</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>food_preferred_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>chicken</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>chicken</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>food_preferred_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>beef</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>beef</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>food_preferred_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>pasta</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>food_preferred_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>vegetables</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>vegetables</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>food_not_preferred_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>pizza</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>pizza</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>food_not_preferred_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>salad</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>salad</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>food_not_preferred_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>sandwich</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>sandwich</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>food_allergies_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>food_allergies_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>food_restrictions_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>food_restrictions_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>False</t>
         </is>
       </c>
     </row>
